--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -486,9 +486,15 @@
       <c r="C3" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -504,9 +510,15 @@
       <c r="C4" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -522,9 +534,15 @@
       <c r="C5" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -540,9 +558,15 @@
       <c r="C6" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,9 +582,15 @@
       <c r="C7" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,215 +606,856 @@
       <c r="C8" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>ARCADE TRADING</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>ARCADE TRADING</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.4762</v>
       </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="n">
         <v>0.5339</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOOKS AND MUCH MORE</t>
+          <t>ZENTRIX INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOOKS AND MUCH MORE</t>
+          <t>ZENTRIX INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAI BABY</t>
+          <t>PUSHP CREATIONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAI BABY</t>
+          <t>PUSHP CREATIONS</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0.4762</v>
       </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="n">
         <v>0.5339</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MECTRONIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MECTRONIC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4762</v>
+        <v>0.5047</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5339</v>
+        <v>0.5593</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE</t>
+          <t>PAL TRADELINK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE</t>
+          <t>PAL TRADELINK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KITSONS KONDAPUR</t>
+          <t>ADVIRAA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KITSONS KONDAPUR</t>
+          <t>ADVIRAA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+          <t>RK Enterprises</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+          <t>RK Enterprises</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4286</v>
+        <v>0.5238</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4915</v>
+        <v>0.5763</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KITSONS GACHIBOWLI</t>
+          <t>Pune Rural Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KITSONS GACHIBOWLI</t>
+          <t>Pune Rural Marketing</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KITSONS GOLDEN MILE</t>
+          <t>POOJA SALES CORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KITSONS GOLDEN MILE</t>
+          <t>POOJA SALES CORP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KITSONS KOKAPET</t>
+          <t>OZI TECHNOLOGIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KITSONS KOKAPET</t>
+          <t>OZI TECHNOLOGIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4915</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+        <v>0.5339</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GOOD LUCK AGENCIES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GOOD LUCK AGENCIES</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G MARKETING</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G MARKETING</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R &amp; S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R &amp; S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ELARA AND COMPANY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ELARA AND COMPANY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MAA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BANSAL BOOK AND STATIONERS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BANSAL BOOK AND STATIONERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TOYS TOWN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TOYS TOWN</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SHREE BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SHREE BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EQUATOR TRADE HOUSE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EQUATOR TRADE HOUSE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MILLENNIUM INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MILLENNIUM INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SK ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SK ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SHUBHAM ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SHUBHAM ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ANAND GIFT EMPORIUM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ANAND GIFT EMPORIUM</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RAJESH TRADERS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RAJESH TRADERS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VIJAY SALES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VIJAY SALES</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEEMA AND SONS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SEEMA AND SONS</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AGGARWAL MARKETING CO.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AGGARWAL MARKETING CO.</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MODERN AGENCIES</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MODERN AGENCIES</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,63 +1456,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="discount" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="discount" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PRINCE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRINCE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.5089</v>
+        <v>0.4738</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4738</v>
+        <v>0.4762</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KIDS JUNCTION</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="discount" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="discount" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +1486,11 @@
           <t>KIDS JUNCTION</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KIDS JUNCTION</t>
+        </is>
+      </c>
       <c r="C45" t="n">
         <v>0.4286</v>
       </c>
@@ -1496,6 +1501,78 @@
         <v>0.4915</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SATNAM MARKETING</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SATNAM MARKETING</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ramdev Extension</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ramdev Extension</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T G ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>T G ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1576,6 +1576,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RAMDEV IMPEX</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RAMDEV IMPEX</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CENTER ONE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CENTER ONE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,6 +1624,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BLISS ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BLISS ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
